--- a/314e-ig/output/StructureDefinition-medicationadministration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-medicationadministration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-medicationadministration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-medicationadministration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-medicationadministration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-medicationadministration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-medicationadministration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-medicationadministration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -734,7 +734,7 @@
     <t>MedicationAdministration.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-patient) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -759,7 +759,7 @@
     <t>MedicationAdministration.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-encounter|EpisodeOfCare) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/encounter-314e|EpisodeOfCare) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -894,7 +894,7 @@
     <t>MedicationAdministration.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Device|4.0.1) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e|http://314e.com/fhir/StructureDefinition/device-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -937,7 +937,7 @@
     <t>MedicationAdministration.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/condition-314e|http://314e.com/fhir/StructureDefinition/condition-diagnosis-314e|http://314e.com/fhir/StructureDefinition/condition-problem-healthconcern-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-notereport-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-lab-314e|http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/observation-lab-general-314e|http://314e.com/fhir/StructureDefinition/observation-microbiology-314e|http://314e.com/fhir/StructureDefinition/observation-microorganism-314e|http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -965,7 +965,7 @@
     <t>MedicationAdministration.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-medicationrequest) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/medicationrequest-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -990,7 +990,7 @@
     <t>MedicationAdministration.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/device-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1177,7 +1177,7 @@
     <t>MedicationAdministration.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance|4.0.1) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(Provenance) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1505,7 +1505,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="131.60546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/314e-ig/output/StructureDefinition-medicationadministration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-medicationadministration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-medicationadministration-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-medicationadministration-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
